--- a/sheet/8618.xlsx
+++ b/sheet/8618.xlsx
@@ -1344,10 +1344,10 @@
         <v>8.5</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>4.53</v>
       </c>
       <c r="H25" t="n">
-        <v>-8.5</v>
+        <v>-3.97</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -2310,10 +2310,10 @@
         <v>73</v>
       </c>
       <c r="C3" t="n">
-        <v>63.57</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>-9.43</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="4">

--- a/sheet/8618.xlsx
+++ b/sheet/8618.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>372</v>
+        <v>1085</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>373</v>
+        <v>1086</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>374</v>
+        <v>1087</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>375</v>
+        <v>1088</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>376</v>
+        <v>1089</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>377</v>
+        <v>1090</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         <v>8.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3.13</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>-5.37</v>
+        <v>-0.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>378</v>
+        <v>1091</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>379</v>
+        <v>1092</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>380</v>
+        <v>1093</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>381</v>
+        <v>1094</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>382</v>
+        <v>1095</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>383</v>
+        <v>1096</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -910,34 +910,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>775</v>
+        <v>1097</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46143</v>
+        <v>46155</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>8.5</v>
       </c>
       <c r="G14" t="n">
-        <v>8.51</v>
+        <v>7.98</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01</v>
+        <v>-0.52</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -950,24 +950,34 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>776</v>
+        <v>1098</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46144</v>
+        <v>46156</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -980,24 +990,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>777</v>
+        <v>1099</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46145</v>
+        <v>46157</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1010,19 +1030,19 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>778</v>
+        <v>1100</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46146</v>
+        <v>46158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1031,13 +1051,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>8.48</v>
+        <v>8.5</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.02</v>
+        <v>0.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1050,34 +1070,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>779</v>
+        <v>1101</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46147</v>
+        <v>46159</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>10:00 PM</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>8.449999999999999</v>
+        <v>13.75</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.05</v>
+        <v>0.75</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1090,34 +1110,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>780</v>
+        <v>1102</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>8.5</v>
       </c>
       <c r="G19" t="n">
-        <v>8.470000000000001</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.03</v>
+        <v>-8.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1130,34 +1150,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>781</v>
+        <v>1103</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>8.5</v>
       </c>
       <c r="G20" t="n">
-        <v>8.6</v>
+        <v>7.95</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1</v>
+        <v>-0.55</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1170,34 +1190,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>782</v>
+        <v>1104</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46150</v>
+        <v>46162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>8.5</v>
       </c>
       <c r="G21" t="n">
-        <v>8.49</v>
+        <v>4.82</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.01</v>
+        <v>-3.68</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1210,7 +1230,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>783</v>
+        <v>2263</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1218,7 +1238,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46151</v>
+        <v>46143</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1227,17 +1247,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>01:00 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="G22" t="n">
-        <v>4.05</v>
+        <v>8.51</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.95</v>
+        <v>0.01</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1250,7 +1270,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>784</v>
+        <v>2264</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1258,7 +1278,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46152</v>
+        <v>46144</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1280,7 +1300,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>785</v>
+        <v>2265</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1288,26 +1308,16 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F24" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>8.52</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1320,7 +1330,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>786</v>
+        <v>2266</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1328,7 +1338,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46154</v>
+        <v>46146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1344,10 +1354,10 @@
         <v>8.5</v>
       </c>
       <c r="G25" t="n">
-        <v>4.53</v>
+        <v>8.48</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.97</v>
+        <v>-0.02</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1360,15 +1370,15 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>961</v>
+        <v>2267</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1384,10 +1394,10 @@
         <v>8.5</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-8.5</v>
+        <v>-0.05</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1400,24 +1410,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>962</v>
+        <v>2268</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46144</v>
+        <v>46148</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1430,24 +1450,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>963</v>
+        <v>2269</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46145</v>
+        <v>46149</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1460,15 +1490,15 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>964</v>
+        <v>2270</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1484,10 +1514,10 @@
         <v>8.5</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>8.49</v>
       </c>
       <c r="H29" t="n">
-        <v>-8.5</v>
+        <v>-0.01</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1500,15 +1530,15 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>965</v>
+        <v>2271</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46147</v>
+        <v>46151</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1517,17 +1547,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>01:00 PM</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="H30" t="n">
-        <v>-8.5</v>
+        <v>-0.95</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1540,34 +1570,24 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>966</v>
+        <v>2272</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F31" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-8.5</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1580,15 +1600,15 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>967</v>
+        <v>2273</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1604,10 +1624,10 @@
         <v>8.5</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>8.52</v>
       </c>
       <c r="H32" t="n">
-        <v>-8.5</v>
+        <v>0.02</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1620,34 +1640,24 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>968</v>
+        <v>2274</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46150</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46154</v>
       </c>
       <c r="F33" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>-8.5</v>
+        <v>4.53</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1660,24 +1670,34 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>969</v>
+        <v>2275</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46151</v>
+        <v>46155</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>8.44</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1690,24 +1710,34 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>970</v>
+        <v>2276</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46152</v>
+        <v>46156</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>8.51</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1720,15 +1750,15 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>971</v>
+        <v>2277</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1744,10 +1774,10 @@
         <v>8.5</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H36" t="n">
-        <v>-8.5</v>
+        <v>-3.7</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1760,34 +1790,24 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>972</v>
+        <v>2278</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F37" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-8.5</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1800,34 +1820,24 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1147</v>
+        <v>2279</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F38" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1840,15 +1850,15 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1148</v>
+        <v>2280</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46144</v>
+        <v>46160</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1857,17 +1867,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>01:00 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="G39" t="n">
-        <v>4.15</v>
+        <v>4.22</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.85</v>
+        <v>-4.28</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1880,24 +1890,34 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1149</v>
+        <v>2281</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46145</v>
+        <v>46161</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1910,15 +1930,15 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1150</v>
+        <v>2282</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46146</v>
+        <v>46162</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1934,10 +1954,10 @@
         <v>8.5</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>3.87</v>
       </c>
       <c r="H41" t="n">
-        <v>-8.5</v>
+        <v>-4.63</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1950,15 +1970,15 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1151</v>
+        <v>2759</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46147</v>
+        <v>46143</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1974,10 +1994,10 @@
         <v>8.5</v>
       </c>
       <c r="G42" t="n">
-        <v>8.550000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H42" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1990,34 +2010,24 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1152</v>
+        <v>2760</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F43" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>8.630000000000001</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2030,34 +2040,24 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1153</v>
+        <v>2761</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F44" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2070,15 +2070,15 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1154</v>
+        <v>2762</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>46150</v>
+        <v>46146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2094,10 +2094,10 @@
         <v>8.5</v>
       </c>
       <c r="G45" t="n">
-        <v>8.6</v>
+        <v>8.58</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2110,21 +2110,31 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1155</v>
+        <v>2763</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>46151</v>
+        <v>46147</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2140,24 +2150,34 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1156</v>
+        <v>2764</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>46152</v>
+        <v>46148</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>8.58</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2170,15 +2190,15 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1157</v>
+        <v>2765</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2194,10 +2214,10 @@
         <v>8.5</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="H48" t="n">
-        <v>-8.5</v>
+        <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2210,41 +2230,1211 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1158</v>
+        <v>2766</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2767</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2768</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2769</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2770</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2771</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2772</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2773</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2774</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2775</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2776</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2777</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2778</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>3131</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>SANCHEZ, ARMANDO [0895]</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C62" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>3132</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>01:00 PM</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>5</v>
+      </c>
+      <c r="G63" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>3133</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>3134</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>3135</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G66" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>3136</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G67" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>3137</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>3138</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>3139</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>3140</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>3141</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="F72" t="n">
+        <v>8</v>
+      </c>
+      <c r="G72" t="n">
+        <v>8</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>3142</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
         <v>46154</v>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
+      <c r="F73" t="n">
+        <v>8</v>
+      </c>
+      <c r="G73" t="n">
+        <v>8</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>3143</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>3144</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>3145</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>3146</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>3147</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>3148</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>3149</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>3150</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G81" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-4.45</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
         <v>8618</v>
       </c>
     </row>
@@ -2291,13 +3481,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68</v>
+        <v>140.5</v>
       </c>
       <c r="C2" t="n">
-        <v>58.38</v>
+        <v>123.75</v>
       </c>
       <c r="D2" t="n">
-        <v>-9.620000000000001</v>
+        <v>-16.75</v>
       </c>
     </row>
     <row r="3">
@@ -2307,13 +3497,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73</v>
+        <v>119.5</v>
       </c>
       <c r="C3" t="n">
-        <v>68.09999999999999</v>
+        <v>110.47</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.9</v>
+        <v>-9.029999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2323,13 +3513,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>93.92</v>
       </c>
       <c r="D4" t="n">
-        <v>-68</v>
+        <v>-25.08</v>
       </c>
     </row>
     <row r="5">
@@ -2339,13 +3529,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="C5" t="n">
-        <v>47.03</v>
+        <v>118.4</v>
       </c>
       <c r="D5" t="n">
-        <v>-25.97</v>
+        <v>-4.6</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8618.xlsx
+++ b/sheet/8618.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1085</v>
+        <v>372</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1086</v>
+        <v>373</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1087</v>
+        <v>374</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1088</v>
+        <v>375</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1089</v>
+        <v>376</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1090</v>
+        <v>377</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         <v>8.5</v>
       </c>
       <c r="G7" t="n">
-        <v>8</v>
+        <v>3.13</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5</v>
+        <v>-5.37</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1091</v>
+        <v>378</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1092</v>
+        <v>379</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1093</v>
+        <v>380</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1094</v>
+        <v>381</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1095</v>
+        <v>382</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1096</v>
+        <v>383</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -910,34 +910,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1097</v>
+        <v>775</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>DUNN, CIERA E [6641]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46155</v>
+        <v>46143</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>05:30 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>8.5</v>
       </c>
       <c r="G14" t="n">
-        <v>7.98</v>
+        <v>8.51</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.52</v>
+        <v>0.01</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -950,34 +950,24 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1098</v>
+        <v>776</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DUNN, CIERA E [6641]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>07:00 AM</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F15" t="n">
-        <v>9.5</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>8.25</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.25</v>
+        <v>0</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -990,34 +980,24 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1099</v>
+        <v>777</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DUNN, CIERA E [6641]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>08:30 AM</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F16" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>9.25</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1030,19 +1010,19 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1100</v>
+        <v>778</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DUNN, CIERA E [6641]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46158</v>
+        <v>46146</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1051,13 +1031,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="G17" t="n">
-        <v>8.5</v>
+        <v>8.48</v>
       </c>
       <c r="H17" t="n">
-        <v>0.5</v>
+        <v>-0.02</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1070,34 +1050,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1101</v>
+        <v>779</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DUNN, CIERA E [6641]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46159</v>
+        <v>46147</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>10:00 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>13</v>
+        <v>8.5</v>
       </c>
       <c r="G18" t="n">
-        <v>13.75</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.75</v>
+        <v>-0.05</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1110,34 +1090,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1102</v>
+        <v>780</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>DUNN, CIERA E [6641]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46160</v>
+        <v>46148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>05:30 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>8.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-8.5</v>
+        <v>-0.03</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1150,34 +1130,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1103</v>
+        <v>781</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>DUNN, CIERA E [6641]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46161</v>
+        <v>46149</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>05:30 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>8.5</v>
       </c>
       <c r="G20" t="n">
-        <v>7.95</v>
+        <v>8.6</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.55</v>
+        <v>0.1</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1190,34 +1170,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1104</v>
+        <v>782</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>DUNN, CIERA E [6641]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46162</v>
+        <v>46150</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>08:30 AM</t>
+          <t>08:00 AM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>05:30 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>8.5</v>
       </c>
       <c r="G21" t="n">
-        <v>4.82</v>
+        <v>8.49</v>
       </c>
       <c r="H21" t="n">
-        <v>-3.68</v>
+        <v>-0.01</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1230,7 +1210,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2263</v>
+        <v>783</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1238,7 +1218,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46143</v>
+        <v>46151</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1247,17 +1227,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>01:00 PM</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="G22" t="n">
-        <v>8.51</v>
+        <v>4.05</v>
       </c>
       <c r="H22" t="n">
-        <v>0.01</v>
+        <v>-0.95</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1270,7 +1250,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2264</v>
+        <v>784</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1278,7 +1258,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46144</v>
+        <v>46152</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1300,7 +1280,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2265</v>
+        <v>785</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1308,16 +1288,26 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46145</v>
+        <v>46153</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>8.52</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1330,7 +1320,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2266</v>
+        <v>786</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1338,7 +1328,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46146</v>
+        <v>46154</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1354,10 +1344,10 @@
         <v>8.5</v>
       </c>
       <c r="G25" t="n">
-        <v>8.48</v>
+        <v>4.53</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.02</v>
+        <v>-3.97</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1370,15 +1360,15 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2267</v>
+        <v>961</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46147</v>
+        <v>46143</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1394,10 +1384,10 @@
         <v>8.5</v>
       </c>
       <c r="G26" t="n">
-        <v>8.449999999999999</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.05</v>
+        <v>-8.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1410,34 +1400,24 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2268</v>
+        <v>962</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F27" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>8.470000000000001</v>
+        <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.03</v>
+        <v>0</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1450,34 +1430,24 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2269</v>
+        <v>963</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F28" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1490,15 +1460,15 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2270</v>
+        <v>964</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46150</v>
+        <v>46146</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1514,10 +1484,10 @@
         <v>8.5</v>
       </c>
       <c r="G29" t="n">
-        <v>8.49</v>
+        <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.01</v>
+        <v>-8.5</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1530,15 +1500,15 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2271</v>
+        <v>965</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46151</v>
+        <v>46147</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1547,17 +1517,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>01:00 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="G30" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.95</v>
+        <v>-8.5</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1570,24 +1540,34 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2272</v>
+        <v>966</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46152</v>
+        <v>46148</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>-8.5</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1600,15 +1580,15 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2273</v>
+        <v>967</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1624,10 +1604,10 @@
         <v>8.5</v>
       </c>
       <c r="G32" t="n">
-        <v>8.52</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.02</v>
+        <v>-8.5</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1640,24 +1620,34 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2274</v>
+        <v>968</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46154</v>
+        <v>46150</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="G33" t="n">
-        <v>8.529999999999999</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>4.53</v>
+        <v>-8.5</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1670,34 +1660,24 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2275</v>
+        <v>969</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F34" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G34" t="n">
-        <v>8.44</v>
+        <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.06</v>
+        <v>0</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1710,34 +1690,24 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2276</v>
+        <v>970</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F35" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G35" t="n">
-        <v>8.51</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1750,15 +1720,15 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2277</v>
+        <v>971</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46157</v>
+        <v>46153</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1774,10 +1744,10 @@
         <v>8.5</v>
       </c>
       <c r="G36" t="n">
-        <v>4.8</v>
+        <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-3.7</v>
+        <v>-8.5</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1790,24 +1760,34 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2278</v>
+        <v>972</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46158</v>
+        <v>46154</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>-8.5</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1820,24 +1800,34 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2279</v>
+        <v>1147</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>SANCHEZ, ARMANDO [0895]</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46159</v>
+        <v>46143</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1850,15 +1840,15 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2280</v>
+        <v>1148</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>SANCHEZ, ARMANDO [0895]</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46160</v>
+        <v>46144</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1867,17 +1857,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>01:00 PM</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="G39" t="n">
-        <v>4.22</v>
+        <v>4.15</v>
       </c>
       <c r="H39" t="n">
-        <v>-4.28</v>
+        <v>-0.85</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1890,34 +1880,24 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2281</v>
+        <v>1149</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>SANCHEZ, ARMANDO [0895]</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F40" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G40" t="n">
-        <v>8.529999999999999</v>
+        <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>0.03</v>
+        <v>0</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1930,15 +1910,15 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2282</v>
+        <v>1150</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>SANCHEZ, ARMANDO [0895]</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46162</v>
+        <v>46146</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1954,10 +1934,10 @@
         <v>8.5</v>
       </c>
       <c r="G41" t="n">
-        <v>3.87</v>
+        <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>-4.63</v>
+        <v>-8.5</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1970,15 +1950,15 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2759</v>
+        <v>1151</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>SANCHEZ, ARMANDO [0895]</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1994,10 +1974,10 @@
         <v>8.5</v>
       </c>
       <c r="G42" t="n">
-        <v>8.5</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2010,24 +1990,34 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2760</v>
+        <v>1152</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>SANCHEZ, ARMANDO [0895]</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46144</v>
+        <v>46148</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2040,24 +2030,34 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2761</v>
+        <v>1153</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>SANCHEZ, ARMANDO [0895]</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>46145</v>
+        <v>46149</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2070,15 +2070,15 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2762</v>
+        <v>1154</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>SANCHEZ, ARMANDO [0895]</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2094,10 +2094,10 @@
         <v>8.5</v>
       </c>
       <c r="G45" t="n">
-        <v>8.58</v>
+        <v>8.6</v>
       </c>
       <c r="H45" t="n">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2110,31 +2110,21 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2763</v>
+        <v>1155</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>SANCHEZ, ARMANDO [0895]</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F46" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2150,34 +2140,24 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2764</v>
+        <v>1156</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>SANCHEZ, ARMANDO [0895]</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F47" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G47" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2190,15 +2170,15 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2765</v>
+        <v>1157</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>SANCHEZ, ARMANDO [0895]</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2214,10 +2194,10 @@
         <v>8.5</v>
       </c>
       <c r="G48" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>-8.5</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2230,15 +2210,15 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2766</v>
+        <v>1158</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>SANCHEZ, ARMANDO [0895]</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2254,10 +2234,10 @@
         <v>8.5</v>
       </c>
       <c r="G49" t="n">
-        <v>8.529999999999999</v>
+        <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>0.03</v>
+        <v>-8.5</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2265,1176 +2245,6 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>2767</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="n">
-        <v>46151</v>
-      </c>
-      <c r="F50" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J50" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>2768</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="n">
-        <v>46152</v>
-      </c>
-      <c r="F51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" t="n">
-        <v>0</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J51" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>2769</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F52" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G52" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="H52" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J52" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>2770</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F53" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G53" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="H53" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J53" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>2771</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F54" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G54" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="H54" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J54" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>2772</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F55" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G55" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J55" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="n">
-        <v>2773</v>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F56" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G56" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J56" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="n">
-        <v>2774</v>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="n">
-        <v>46158</v>
-      </c>
-      <c r="F57" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J57" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="n">
-        <v>2775</v>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="n">
-        <v>46159</v>
-      </c>
-      <c r="F58" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J58" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n">
-        <v>2776</v>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F59" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G59" t="n">
-        <v>0</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J59" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n">
-        <v>2777</v>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F60" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G60" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J60" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>2778</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F61" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G61" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J61" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>3131</v>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F62" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G62" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="H62" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J62" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>3132</v>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="n">
-        <v>46144</v>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>01:00 PM</t>
-        </is>
-      </c>
-      <c r="F63" t="n">
-        <v>5</v>
-      </c>
-      <c r="G63" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-0.85</v>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J63" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>3133</v>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="n">
-        <v>46145</v>
-      </c>
-      <c r="F64" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" t="n">
-        <v>0</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J64" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>3134</v>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F65" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G65" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I65" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J65" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="n">
-        <v>3135</v>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F66" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G66" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J66" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="n">
-        <v>3136</v>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F67" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G67" t="n">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J67" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="n">
-        <v>3137</v>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F68" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G68" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="H68" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J68" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>3138</v>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="n">
-        <v>46150</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F69" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G69" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J69" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="n">
-        <v>3139</v>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="n">
-        <v>46151</v>
-      </c>
-      <c r="F70" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J70" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n">
-        <v>3140</v>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="n">
-        <v>46152</v>
-      </c>
-      <c r="F71" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J71" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n">
-        <v>3141</v>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="F72" t="n">
-        <v>8</v>
-      </c>
-      <c r="G72" t="n">
-        <v>8</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J72" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n">
-        <v>3142</v>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="F73" t="n">
-        <v>8</v>
-      </c>
-      <c r="G73" t="n">
-        <v>8</v>
-      </c>
-      <c r="H73" t="n">
-        <v>0</v>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J73" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="n">
-        <v>3143</v>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F74" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G74" t="n">
-        <v>8.58</v>
-      </c>
-      <c r="H74" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J74" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="n">
-        <v>3144</v>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F75" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G75" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="H75" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J75" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="n">
-        <v>3145</v>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F76" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G76" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="H76" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J76" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="n">
-        <v>3146</v>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="n">
-        <v>46158</v>
-      </c>
-      <c r="F77" t="n">
-        <v>0</v>
-      </c>
-      <c r="G77" t="n">
-        <v>0</v>
-      </c>
-      <c r="H77" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J77" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="n">
-        <v>3147</v>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="n">
-        <v>46159</v>
-      </c>
-      <c r="F78" t="n">
-        <v>0</v>
-      </c>
-      <c r="G78" t="n">
-        <v>0</v>
-      </c>
-      <c r="H78" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J78" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="n">
-        <v>3148</v>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F79" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G79" t="n">
-        <v>8.550000000000001</v>
-      </c>
-      <c r="H79" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J79" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="n">
-        <v>3149</v>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F80" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G80" t="n">
-        <v>8.460000000000001</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-0.04</v>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J80" t="n">
-        <v>8618</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="n">
-        <v>3150</v>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="n">
-        <v>46162</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G81" t="n">
-        <v>4.05</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-4.45</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
         <v>8618</v>
       </c>
     </row>
@@ -3481,13 +2291,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>140.5</v>
+        <v>68</v>
       </c>
       <c r="C2" t="n">
-        <v>123.75</v>
+        <v>58.38</v>
       </c>
       <c r="D2" t="n">
-        <v>-16.75</v>
+        <v>-9.620000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -3497,13 +2307,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>119.5</v>
+        <v>73</v>
       </c>
       <c r="C3" t="n">
-        <v>110.47</v>
+        <v>68.09999999999999</v>
       </c>
       <c r="D3" t="n">
-        <v>-9.029999999999999</v>
+        <v>-4.9</v>
       </c>
     </row>
     <row r="4">
@@ -3513,13 +2323,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>119</v>
+        <v>68</v>
       </c>
       <c r="C4" t="n">
-        <v>93.92</v>
+        <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>-25.08</v>
+        <v>-68</v>
       </c>
     </row>
     <row r="5">
@@ -3529,13 +2339,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>123</v>
+        <v>73</v>
       </c>
       <c r="C5" t="n">
-        <v>118.4</v>
+        <v>47.03</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.6</v>
+        <v>-25.97</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8618.xlsx
+++ b/sheet/8618.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J49"/>
+  <dimension ref="A1:J81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>372</v>
+        <v>1085</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>373</v>
+        <v>1086</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>374</v>
+        <v>1087</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>375</v>
+        <v>1088</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>376</v>
+        <v>1089</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>377</v>
+        <v>1090</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         <v>8.5</v>
       </c>
       <c r="G7" t="n">
-        <v>3.13</v>
+        <v>8</v>
       </c>
       <c r="H7" t="n">
-        <v>-5.37</v>
+        <v>-0.5</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>378</v>
+        <v>1091</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>379</v>
+        <v>1092</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>380</v>
+        <v>1093</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>381</v>
+        <v>1094</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>382</v>
+        <v>1095</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>383</v>
+        <v>1096</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -910,34 +910,34 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>775</v>
+        <v>1097</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C14" s="2" t="n">
-        <v>46143</v>
+        <v>46155</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F14" t="n">
         <v>8.5</v>
       </c>
       <c r="G14" t="n">
-        <v>8.51</v>
+        <v>7.98</v>
       </c>
       <c r="H14" t="n">
-        <v>0.01</v>
+        <v>-0.52</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -950,24 +950,34 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>776</v>
+        <v>1098</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
-        <v>46144</v>
+        <v>46156</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>07:00 AM</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>8.25</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
@@ -980,24 +990,34 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>777</v>
+        <v>1099</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
-        <v>46145</v>
+        <v>46157</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>08:30 AM</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>9.25</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1010,19 +1030,19 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>778</v>
+        <v>1100</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C17" s="2" t="n">
-        <v>46146</v>
+        <v>46158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1031,13 +1051,13 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="G17" t="n">
-        <v>8.48</v>
+        <v>8.5</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.02</v>
+        <v>0.5</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1050,34 +1070,34 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>779</v>
+        <v>1101</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C18" s="2" t="n">
-        <v>46147</v>
+        <v>46159</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>10:00 PM</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>8.5</v>
+        <v>13</v>
       </c>
       <c r="G18" t="n">
-        <v>8.449999999999999</v>
+        <v>13.75</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.05</v>
+        <v>0.75</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1090,34 +1110,34 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>780</v>
+        <v>1102</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C19" s="2" t="n">
-        <v>46148</v>
+        <v>46160</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F19" t="n">
         <v>8.5</v>
       </c>
       <c r="G19" t="n">
-        <v>8.470000000000001</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.03</v>
+        <v>-8.5</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1130,34 +1150,34 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>781</v>
+        <v>1103</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C20" s="2" t="n">
-        <v>46149</v>
+        <v>46161</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F20" t="n">
         <v>8.5</v>
       </c>
       <c r="G20" t="n">
-        <v>8.6</v>
+        <v>7.95</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1</v>
+        <v>-0.55</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
@@ -1170,34 +1190,34 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>782</v>
+        <v>1104</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C21" s="2" t="n">
-        <v>46150</v>
+        <v>46162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F21" t="n">
         <v>8.5</v>
       </c>
       <c r="G21" t="n">
-        <v>8.49</v>
+        <v>8.02</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.01</v>
+        <v>-0.48</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
@@ -1210,7 +1230,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>783</v>
+        <v>2263</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1218,7 +1238,7 @@
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46151</v>
+        <v>46143</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1227,17 +1247,17 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>01:00 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="G22" t="n">
-        <v>4.05</v>
+        <v>8.51</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.95</v>
+        <v>0.01</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1250,7 +1270,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>784</v>
+        <v>2264</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1258,7 +1278,7 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46152</v>
+        <v>46144</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1280,7 +1300,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>785</v>
+        <v>2265</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1288,26 +1308,16 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F24" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G24" t="n">
-        <v>8.52</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1320,7 +1330,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>786</v>
+        <v>2266</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1328,7 +1338,7 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46154</v>
+        <v>46146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1344,10 +1354,10 @@
         <v>8.5</v>
       </c>
       <c r="G25" t="n">
-        <v>4.53</v>
+        <v>8.48</v>
       </c>
       <c r="H25" t="n">
-        <v>-3.97</v>
+        <v>-0.02</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1360,15 +1370,15 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>961</v>
+        <v>2267</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1384,10 +1394,10 @@
         <v>8.5</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="H26" t="n">
-        <v>-8.5</v>
+        <v>-0.05</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1400,24 +1410,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>962</v>
+        <v>2268</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46144</v>
+        <v>46148</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>-0.03</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1430,24 +1450,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>963</v>
+        <v>2269</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46145</v>
+        <v>46149</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1460,15 +1490,15 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>964</v>
+        <v>2270</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46146</v>
+        <v>46150</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1484,10 +1514,10 @@
         <v>8.5</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>8.49</v>
       </c>
       <c r="H29" t="n">
-        <v>-8.5</v>
+        <v>-0.01</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1500,15 +1530,15 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>965</v>
+        <v>2271</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46147</v>
+        <v>46151</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1517,17 +1547,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>01:00 PM</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="H30" t="n">
-        <v>-8.5</v>
+        <v>-0.95</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1540,34 +1570,24 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>966</v>
+        <v>2272</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F31" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-8.5</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1580,15 +1600,15 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>967</v>
+        <v>2273</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1604,10 +1624,10 @@
         <v>8.5</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>8.52</v>
       </c>
       <c r="H32" t="n">
-        <v>-8.5</v>
+        <v>0.02</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1620,34 +1640,24 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>968</v>
+        <v>2274</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46150</v>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46154</v>
       </c>
       <c r="F33" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H33" t="n">
-        <v>-8.5</v>
+        <v>4.53</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1660,24 +1670,34 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>969</v>
+        <v>2275</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46151</v>
+        <v>46155</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F34" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G34" t="n">
-        <v>0</v>
+        <v>8.44</v>
       </c>
       <c r="H34" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1690,24 +1710,34 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>970</v>
+        <v>2276</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46152</v>
+        <v>46156</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F35" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G35" t="n">
-        <v>0</v>
+        <v>8.51</v>
       </c>
       <c r="H35" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1720,15 +1750,15 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>971</v>
+        <v>2277</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46153</v>
+        <v>46157</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1744,10 +1774,10 @@
         <v>8.5</v>
       </c>
       <c r="G36" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H36" t="n">
-        <v>-8.5</v>
+        <v>-3.7</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1760,34 +1790,24 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>972</v>
+        <v>2278</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F37" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-8.5</v>
+        <v>0</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1800,34 +1820,24 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1147</v>
+        <v>2279</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46143</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F38" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G38" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1840,15 +1850,15 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1148</v>
+        <v>2280</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46144</v>
+        <v>46160</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1857,17 +1867,17 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>01:00 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F39" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="G39" t="n">
-        <v>4.15</v>
+        <v>4.22</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.85</v>
+        <v>-4.28</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1880,24 +1890,34 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>1149</v>
+        <v>2281</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46145</v>
+        <v>46161</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F40" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G40" t="n">
-        <v>0</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1910,15 +1930,15 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1150</v>
+        <v>2282</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46146</v>
+        <v>46162</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1934,10 +1954,10 @@
         <v>8.5</v>
       </c>
       <c r="G41" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="H41" t="n">
-        <v>-8.5</v>
+        <v>0</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1950,15 +1970,15 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>1151</v>
+        <v>2759</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46147</v>
+        <v>46143</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1974,10 +1994,10 @@
         <v>8.5</v>
       </c>
       <c r="G42" t="n">
-        <v>8.550000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H42" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -1990,34 +2010,24 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>1152</v>
+        <v>2760</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F43" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G43" t="n">
-        <v>8.630000000000001</v>
+        <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2030,34 +2040,24 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>1153</v>
+        <v>2761</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>46149</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F44" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G44" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2070,15 +2070,15 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1154</v>
+        <v>2762</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>46150</v>
+        <v>46146</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2094,10 +2094,10 @@
         <v>8.5</v>
       </c>
       <c r="G45" t="n">
-        <v>8.6</v>
+        <v>8.58</v>
       </c>
       <c r="H45" t="n">
-        <v>0.1</v>
+        <v>0.08</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2110,21 +2110,31 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>1155</v>
+        <v>2763</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>46151</v>
+        <v>46147</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F46" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G46" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2140,24 +2150,34 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>1156</v>
+        <v>2764</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>46152</v>
+        <v>46148</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F47" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G47" t="n">
-        <v>0</v>
+        <v>8.58</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2170,15 +2190,15 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>1157</v>
+        <v>2765</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46153</v>
+        <v>46149</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2194,10 +2214,10 @@
         <v>8.5</v>
       </c>
       <c r="G48" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="H48" t="n">
-        <v>-8.5</v>
+        <v>0</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2210,41 +2230,1211 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>1158</v>
+        <v>2766</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G49" t="n">
+        <v>8.529999999999999</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J49" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2767</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J50" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2768</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J51" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2769</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F52" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G52" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J52" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2770</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F53" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G53" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J53" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2771</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F54" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G54" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J54" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2772</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F55" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G55" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J55" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2773</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F56" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G56" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J56" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2774</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J57" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2775</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J58" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2776</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F59" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J59" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2777</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F60" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J60" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2778</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F61" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J61" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>3131</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
           <t>SANCHEZ, ARMANDO [0895]</t>
         </is>
       </c>
-      <c r="C49" s="2" t="n">
+      <c r="C62" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F62" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G62" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J62" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>3132</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>01:00 PM</t>
+        </is>
+      </c>
+      <c r="F63" t="n">
+        <v>5</v>
+      </c>
+      <c r="G63" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J63" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>3133</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J64" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>3134</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F65" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G65" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J65" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>3135</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F66" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G66" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J66" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>3136</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F67" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G67" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J67" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>3137</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F68" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G68" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J68" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>3138</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F69" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G69" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J69" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>3139</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J70" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>3140</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J71" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>3141</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="F72" t="n">
+        <v>8</v>
+      </c>
+      <c r="G72" t="n">
+        <v>8</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J72" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>3142</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="n">
         <v>46154</v>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F49" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G49" t="n">
-        <v>0</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-8.5</v>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J49" t="n">
+      <c r="F73" t="n">
+        <v>8</v>
+      </c>
+      <c r="G73" t="n">
+        <v>8</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J73" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>3143</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F74" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G74" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J74" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>3144</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F75" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G75" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J75" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>3145</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F76" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G76" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J76" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>3146</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J77" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>3147</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J78" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>3148</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F79" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G79" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J79" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>3149</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F80" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G80" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="H80" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J80" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>3150</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F81" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G81" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
         <v>8618</v>
       </c>
     </row>
@@ -2291,13 +3481,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>68</v>
+        <v>140.5</v>
       </c>
       <c r="C2" t="n">
-        <v>58.38</v>
+        <v>126.95</v>
       </c>
       <c r="D2" t="n">
-        <v>-9.620000000000001</v>
+        <v>-13.55</v>
       </c>
     </row>
     <row r="3">
@@ -2307,13 +3497,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>73</v>
+        <v>119.5</v>
       </c>
       <c r="C3" t="n">
-        <v>68.09999999999999</v>
+        <v>115.1</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.9</v>
+        <v>-4.399999999999999</v>
       </c>
     </row>
     <row r="4">
@@ -2323,13 +3513,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>68</v>
+        <v>119</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>93.92</v>
       </c>
       <c r="D4" t="n">
-        <v>-68</v>
+        <v>-25.08</v>
       </c>
     </row>
     <row r="5">
@@ -2339,13 +3529,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>73</v>
+        <v>123</v>
       </c>
       <c r="C5" t="n">
-        <v>47.03</v>
+        <v>122.85</v>
       </c>
       <c r="D5" t="n">
-        <v>-25.97</v>
+        <v>-0.1499999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8618.xlsx
+++ b/sheet/8618.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J81"/>
+  <dimension ref="A1:J85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1230,34 +1230,34 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2263</v>
+        <v>1105</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C22" s="2" t="n">
-        <v>46143</v>
+        <v>46163</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F22" t="n">
         <v>8.5</v>
       </c>
       <c r="G22" t="n">
-        <v>8.51</v>
+        <v>4.83</v>
       </c>
       <c r="H22" t="n">
-        <v>0.01</v>
+        <v>-3.67</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2264</v>
+        <v>2263</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1278,16 +1278,26 @@
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46144</v>
+        <v>46143</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>8.51</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1300,7 +1310,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2265</v>
+        <v>2264</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1308,7 +1318,7 @@
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46145</v>
+        <v>46144</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1330,7 +1340,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2266</v>
+        <v>2265</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1338,26 +1348,16 @@
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F25" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G25" t="n">
-        <v>8.48</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1370,7 +1370,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2267</v>
+        <v>2266</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1378,7 +1378,7 @@
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46147</v>
+        <v>46146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -1394,10 +1394,10 @@
         <v>8.5</v>
       </c>
       <c r="G26" t="n">
-        <v>8.449999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1410,7 +1410,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2268</v>
+        <v>2267</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46148</v>
+        <v>46147</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1434,10 +1434,10 @@
         <v>8.5</v>
       </c>
       <c r="G27" t="n">
-        <v>8.470000000000001</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.03</v>
+        <v>-0.05</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2269</v>
+        <v>2268</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
@@ -1458,7 +1458,7 @@
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46149</v>
+        <v>46148</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1474,10 +1474,10 @@
         <v>8.5</v>
       </c>
       <c r="G28" t="n">
-        <v>8.6</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="H28" t="n">
-        <v>0.1</v>
+        <v>-0.03</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1490,7 +1490,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2270</v>
+        <v>2269</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
@@ -1498,7 +1498,7 @@
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46150</v>
+        <v>46149</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -1514,10 +1514,10 @@
         <v>8.5</v>
       </c>
       <c r="G29" t="n">
-        <v>8.49</v>
+        <v>8.6</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.01</v>
+        <v>0.1</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2271</v>
+        <v>2270</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46151</v>
+        <v>46150</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1547,17 +1547,17 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>01:00 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F30" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="G30" t="n">
-        <v>4.05</v>
+        <v>8.49</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.95</v>
+        <v>-0.01</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2272</v>
+        <v>2271</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1578,16 +1578,26 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46152</v>
+        <v>46151</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>01:00 PM</t>
+        </is>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>-0.95</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1600,7 +1610,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2273</v>
+        <v>2272</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1608,26 +1618,16 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F32" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G32" t="n">
-        <v>8.52</v>
+        <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1640,7 +1640,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2274</v>
+        <v>2273</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1648,16 +1648,26 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46154</v>
+        <v>46153</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F33" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="G33" t="n">
-        <v>8.529999999999999</v>
+        <v>8.52</v>
       </c>
       <c r="H33" t="n">
-        <v>4.53</v>
+        <v>0.02</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1670,7 +1680,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2275</v>
+        <v>2274</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1678,26 +1688,16 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46154</v>
       </c>
       <c r="F34" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="G34" t="n">
-        <v>8.44</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.06</v>
+        <v>4.53</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2276</v>
+        <v>2275</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46156</v>
+        <v>46155</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1734,10 +1734,10 @@
         <v>8.5</v>
       </c>
       <c r="G35" t="n">
-        <v>8.51</v>
+        <v>8.44</v>
       </c>
       <c r="H35" t="n">
-        <v>0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2277</v>
+        <v>2276</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46157</v>
+        <v>46156</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>8.5</v>
       </c>
       <c r="G36" t="n">
-        <v>4.8</v>
+        <v>8.51</v>
       </c>
       <c r="H36" t="n">
-        <v>-3.7</v>
+        <v>0.01</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2278</v>
+        <v>2277</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1798,16 +1798,26 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46158</v>
+        <v>46157</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F37" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G37" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="H37" t="n">
-        <v>0</v>
+        <v>-3.7</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1820,7 +1830,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2279</v>
+        <v>2278</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1828,7 +1838,7 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46159</v>
+        <v>46158</v>
       </c>
       <c r="F38" t="n">
         <v>0</v>
@@ -1850,7 +1860,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2280</v>
+        <v>2279</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1858,26 +1868,16 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F39" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G39" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-4.28</v>
+        <v>0</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
@@ -1890,7 +1890,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2281</v>
+        <v>2280</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1898,7 +1898,7 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46161</v>
+        <v>46160</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1914,10 +1914,10 @@
         <v>8.5</v>
       </c>
       <c r="G40" t="n">
-        <v>8.529999999999999</v>
+        <v>4.22</v>
       </c>
       <c r="H40" t="n">
-        <v>0.03</v>
+        <v>-4.28</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2282</v>
+        <v>2281</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1938,7 +1938,7 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46162</v>
+        <v>46161</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -1954,10 +1954,10 @@
         <v>8.5</v>
       </c>
       <c r="G41" t="n">
-        <v>8.5</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1970,15 +1970,15 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2759</v>
+        <v>2282</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46143</v>
+        <v>46162</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2010,24 +2010,34 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2760</v>
+        <v>2283</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46144</v>
+        <v>46163</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F43" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G43" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="H43" t="n">
-        <v>0</v>
+        <v>-4.45</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2040,7 +2050,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2761</v>
+        <v>2759</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
@@ -2048,13 +2058,23 @@
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>46145</v>
+        <v>46143</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F44" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G44" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="H44" t="n">
         <v>0</v>
@@ -2070,7 +2090,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2762</v>
+        <v>2760</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
@@ -2078,26 +2098,16 @@
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>46146</v>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F45" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2110,7 +2120,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2763</v>
+        <v>2761</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
@@ -2118,23 +2128,13 @@
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>46147</v>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F46" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G46" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H46" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2764</v>
+        <v>2762</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
@@ -2158,7 +2158,7 @@
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>46148</v>
+        <v>46146</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2765</v>
+        <v>2763</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
@@ -2198,7 +2198,7 @@
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46149</v>
+        <v>46147</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2766</v>
+        <v>2764</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -2238,7 +2238,7 @@
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>46150</v>
+        <v>46148</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2254,10 +2254,10 @@
         <v>8.5</v>
       </c>
       <c r="G49" t="n">
-        <v>8.529999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="H49" t="n">
-        <v>0.03</v>
+        <v>0.08</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2270,7 +2270,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -2278,13 +2278,23 @@
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>46151</v>
+        <v>46149</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F50" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G50" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="H50" t="n">
         <v>0</v>
@@ -2300,7 +2310,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2768</v>
+        <v>2766</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
@@ -2308,16 +2318,26 @@
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>46152</v>
+        <v>46150</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F51" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H51" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2330,7 +2350,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2769</v>
+        <v>2767</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
@@ -2338,26 +2358,16 @@
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>46153</v>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F52" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G52" t="n">
-        <v>8.57</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2370,7 +2380,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2770</v>
+        <v>2768</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
@@ -2378,26 +2388,16 @@
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>46154</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F53" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G53" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2771</v>
+        <v>2769</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
@@ -2418,7 +2418,7 @@
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>46155</v>
+        <v>46153</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2434,10 +2434,10 @@
         <v>8.5</v>
       </c>
       <c r="G54" t="n">
-        <v>8.58</v>
+        <v>8.57</v>
       </c>
       <c r="H54" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2450,7 +2450,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2772</v>
+        <v>2770</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2474,10 +2474,10 @@
         <v>8.5</v>
       </c>
       <c r="G55" t="n">
-        <v>8.5</v>
+        <v>8.58</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2490,7 +2490,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2773</v>
+        <v>2771</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>46157</v>
+        <v>46155</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2514,10 +2514,10 @@
         <v>8.5</v>
       </c>
       <c r="G56" t="n">
-        <v>8.5</v>
+        <v>8.58</v>
       </c>
       <c r="H56" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2530,7 +2530,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2774</v>
+        <v>2772</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
@@ -2538,13 +2538,23 @@
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>46158</v>
+        <v>46156</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F57" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G57" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="H57" t="n">
         <v>0</v>
@@ -2560,7 +2570,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2775</v>
+        <v>2773</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2568,13 +2578,23 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>46159</v>
+        <v>46157</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F58" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G58" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="H58" t="n">
         <v>0</v>
@@ -2590,7 +2610,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2776</v>
+        <v>2774</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2598,26 +2618,16 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>46160</v>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F59" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>-8.5</v>
+        <v>0</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -2630,7 +2640,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2777</v>
+        <v>2775</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2638,26 +2648,16 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46159</v>
       </c>
       <c r="F60" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>-8.5</v>
+        <v>0</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2778</v>
+        <v>2776</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2678,7 +2678,7 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2710,15 +2710,15 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>3131</v>
+        <v>2777</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>46143</v>
+        <v>46161</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2734,10 +2734,10 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>0.05</v>
+        <v>-8.5</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -2750,15 +2750,15 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>3132</v>
+        <v>2778</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>46144</v>
+        <v>46162</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2767,17 +2767,17 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>01:00 PM</t>
+          <t>05:00 PM</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>5</v>
+        <v>8.5</v>
       </c>
       <c r="G63" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>-0.85</v>
+        <v>-8.5</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -2790,24 +2790,34 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>3133</v>
+        <v>2779</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>46145</v>
+        <v>46163</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F64" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>-8.5</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -2820,7 +2830,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>3134</v>
+        <v>3131</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
@@ -2828,7 +2838,7 @@
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>46146</v>
+        <v>46143</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2844,10 +2854,10 @@
         <v>8.5</v>
       </c>
       <c r="G65" t="n">
-        <v>8.56</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H65" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -2860,7 +2870,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>3135</v>
+        <v>3132</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
@@ -2868,7 +2878,7 @@
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>46147</v>
+        <v>46144</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2877,17 +2887,17 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>01:00 PM</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>8.5</v>
+        <v>5</v>
       </c>
       <c r="G66" t="n">
-        <v>8.550000000000001</v>
+        <v>4.15</v>
       </c>
       <c r="H66" t="n">
-        <v>0.05</v>
+        <v>-0.85</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -2900,7 +2910,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>3136</v>
+        <v>3133</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
@@ -2908,26 +2918,16 @@
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>46148</v>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46145</v>
       </c>
       <c r="F67" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G67" t="n">
-        <v>8.630000000000001</v>
+        <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>0.13</v>
+        <v>0</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -2940,7 +2940,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>3137</v>
+        <v>3134</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
@@ -2948,7 +2948,7 @@
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>46149</v>
+        <v>46146</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2964,10 +2964,10 @@
         <v>8.5</v>
       </c>
       <c r="G68" t="n">
-        <v>8.550000000000001</v>
+        <v>8.56</v>
       </c>
       <c r="H68" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -2980,7 +2980,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>3138</v>
+        <v>3135</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
@@ -2988,7 +2988,7 @@
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>46150</v>
+        <v>46147</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3004,10 +3004,10 @@
         <v>8.5</v>
       </c>
       <c r="G69" t="n">
-        <v>8.6</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H69" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>3139</v>
+        <v>3136</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
@@ -3028,16 +3028,26 @@
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>46151</v>
+        <v>46148</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F70" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G70" t="n">
-        <v>0</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>0.13</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3050,7 +3060,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>3140</v>
+        <v>3137</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
@@ -3058,16 +3068,26 @@
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>46152</v>
+        <v>46149</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F71" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G71" t="n">
-        <v>0</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="H71" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3080,7 +3100,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>3141</v>
+        <v>3138</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
@@ -3088,16 +3108,26 @@
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>46153</v>
+        <v>46150</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F72" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="G72" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="H72" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3110,7 +3140,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>3142</v>
+        <v>3139</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
@@ -3118,13 +3148,13 @@
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>46154</v>
+        <v>46151</v>
       </c>
       <c r="F73" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G73" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H73" t="n">
         <v>0</v>
@@ -3140,7 +3170,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>3143</v>
+        <v>3140</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
@@ -3148,26 +3178,16 @@
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>46155</v>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46152</v>
       </c>
       <c r="F74" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G74" t="n">
-        <v>8.58</v>
+        <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3180,7 +3200,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>3144</v>
+        <v>3141</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
@@ -3188,26 +3208,16 @@
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>46156</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46153</v>
       </c>
       <c r="F75" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="G75" t="n">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="H75" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3220,7 +3230,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>3145</v>
+        <v>3142</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
@@ -3228,26 +3238,16 @@
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>46157</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46154</v>
       </c>
       <c r="F76" t="n">
-        <v>8.5</v>
+        <v>8</v>
       </c>
       <c r="G76" t="n">
-        <v>8.57</v>
+        <v>8</v>
       </c>
       <c r="H76" t="n">
-        <v>0.07000000000000001</v>
+        <v>0</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3260,7 +3260,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>3146</v>
+        <v>3143</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
@@ -3268,16 +3268,26 @@
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>46158</v>
+        <v>46155</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F77" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G77" t="n">
-        <v>0</v>
+        <v>8.58</v>
       </c>
       <c r="H77" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3290,7 +3300,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
@@ -3298,16 +3308,26 @@
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>46159</v>
+        <v>46156</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F78" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G78" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="H78" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3320,7 +3340,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>3148</v>
+        <v>3145</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
@@ -3328,7 +3348,7 @@
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>46160</v>
+        <v>46157</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3344,10 +3364,10 @@
         <v>8.5</v>
       </c>
       <c r="G79" t="n">
-        <v>8.550000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="H79" t="n">
-        <v>0.05</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3360,7 +3380,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>3149</v>
+        <v>3146</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
@@ -3368,26 +3388,16 @@
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46158</v>
       </c>
       <c r="F80" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="G80" t="n">
-        <v>8.460000000000001</v>
+        <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -3400,41 +3410,191 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
+        <v>3147</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J81" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>3148</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F82" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G82" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J82" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>3149</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F83" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G83" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J83" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
         <v>3150</v>
       </c>
-      <c r="B81" t="inlineStr">
+      <c r="B84" t="inlineStr">
         <is>
           <t>SANCHEZ, ARMANDO [0895]</t>
         </is>
       </c>
-      <c r="C81" s="2" t="n">
+      <c r="C84" s="2" t="n">
         <v>46162</v>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F81" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G81" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="H81" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J81" t="n">
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F84" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G84" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J84" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>3151</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G85" t="n">
+        <v>4.03</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-4.47</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
         <v>8618</v>
       </c>
     </row>
@@ -3481,13 +3641,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>140.5</v>
+        <v>149</v>
       </c>
       <c r="C2" t="n">
-        <v>126.95</v>
+        <v>131.78</v>
       </c>
       <c r="D2" t="n">
-        <v>-13.55</v>
+        <v>-17.22</v>
       </c>
     </row>
     <row r="3">
@@ -3497,13 +3657,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>119.5</v>
+        <v>128</v>
       </c>
       <c r="C3" t="n">
-        <v>115.1</v>
+        <v>119.15</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.399999999999999</v>
+        <v>-8.85</v>
       </c>
     </row>
     <row r="4">
@@ -3513,13 +3673,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>119</v>
+        <v>127.5</v>
       </c>
       <c r="C4" t="n">
         <v>93.92</v>
       </c>
       <c r="D4" t="n">
-        <v>-25.08</v>
+        <v>-33.58</v>
       </c>
     </row>
     <row r="5">
@@ -3529,13 +3689,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>123</v>
+        <v>131.5</v>
       </c>
       <c r="C5" t="n">
-        <v>122.85</v>
+        <v>126.88</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1499999999999999</v>
+        <v>-4.619999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8618.xlsx
+++ b/sheet/8618.xlsx
@@ -1254,10 +1254,10 @@
         <v>8.5</v>
       </c>
       <c r="G22" t="n">
-        <v>4.83</v>
+        <v>8.029999999999999</v>
       </c>
       <c r="H22" t="n">
-        <v>-3.67</v>
+        <v>-0.47</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -2034,10 +2034,10 @@
         <v>8.5</v>
       </c>
       <c r="G43" t="n">
-        <v>4.05</v>
+        <v>8.57</v>
       </c>
       <c r="H43" t="n">
-        <v>-4.45</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -3584,10 +3584,10 @@
         <v>8.5</v>
       </c>
       <c r="G85" t="n">
-        <v>4.03</v>
+        <v>8.48</v>
       </c>
       <c r="H85" t="n">
-        <v>-4.47</v>
+        <v>-0.02</v>
       </c>
       <c r="I85" t="inlineStr">
         <is>
@@ -3644,10 +3644,10 @@
         <v>149</v>
       </c>
       <c r="C2" t="n">
-        <v>131.78</v>
+        <v>134.98</v>
       </c>
       <c r="D2" t="n">
-        <v>-17.22</v>
+        <v>-14.02</v>
       </c>
     </row>
     <row r="3">
@@ -3660,10 +3660,10 @@
         <v>128</v>
       </c>
       <c r="C3" t="n">
-        <v>119.15</v>
+        <v>123.67</v>
       </c>
       <c r="D3" t="n">
-        <v>-8.85</v>
+        <v>-4.33</v>
       </c>
     </row>
     <row r="4">
@@ -3692,10 +3692,10 @@
         <v>131.5</v>
       </c>
       <c r="C5" t="n">
-        <v>126.88</v>
+        <v>131.33</v>
       </c>
       <c r="D5" t="n">
-        <v>-4.619999999999999</v>
+        <v>-0.1699999999999999</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8618.xlsx
+++ b/sheet/8618.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J85"/>
+  <dimension ref="A1:J113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -470,7 +470,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1085</v>
+        <v>1054</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -510,7 +510,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1086</v>
+        <v>1055</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -540,7 +540,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1087</v>
+        <v>1056</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -570,7 +570,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1088</v>
+        <v>1057</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -610,7 +610,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1089</v>
+        <v>1058</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
@@ -650,7 +650,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1090</v>
+        <v>1059</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
@@ -690,7 +690,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1091</v>
+        <v>1060</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1092</v>
+        <v>1061</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
@@ -770,7 +770,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1093</v>
+        <v>1062</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1094</v>
+        <v>1063</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -830,7 +830,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1095</v>
+        <v>1064</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
@@ -870,7 +870,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1096</v>
+        <v>1065</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -910,7 +910,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1097</v>
+        <v>1066</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1098</v>
+        <v>1067</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1099</v>
+        <v>1068</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -1030,7 +1030,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1100</v>
+        <v>1069</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -1070,7 +1070,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1101</v>
+        <v>1070</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1110,7 +1110,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1102</v>
+        <v>1071</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1134,10 +1134,10 @@
         <v>8.5</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>4.47</v>
       </c>
       <c r="H19" t="n">
-        <v>-8.5</v>
+        <v>-4.03</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1103</v>
+        <v>1072</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1190,7 +1190,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1104</v>
+        <v>1073</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1230,7 +1230,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1105</v>
+        <v>1074</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1270,34 +1270,34 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2263</v>
+        <v>1075</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C23" s="2" t="n">
-        <v>46143</v>
+        <v>46164</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F23" t="n">
         <v>8.5</v>
       </c>
       <c r="G23" t="n">
-        <v>8.51</v>
+        <v>8.1</v>
       </c>
       <c r="H23" t="n">
-        <v>0.01</v>
+        <v>-0.4</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
@@ -1310,15 +1310,15 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2264</v>
+        <v>1076</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C24" s="2" t="n">
-        <v>46144</v>
+        <v>46165</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -1340,15 +1340,15 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2265</v>
+        <v>1077</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C25" s="2" t="n">
-        <v>46145</v>
+        <v>46166</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -1370,34 +1370,34 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2266</v>
+        <v>1078</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C26" s="2" t="n">
-        <v>46146</v>
+        <v>46167</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F26" t="n">
         <v>8.5</v>
       </c>
       <c r="G26" t="n">
-        <v>8.48</v>
+        <v>7</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.02</v>
+        <v>-1.5</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
@@ -1410,34 +1410,34 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2267</v>
+        <v>1079</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C27" s="2" t="n">
-        <v>46147</v>
+        <v>46168</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F27" t="n">
         <v>8.5</v>
       </c>
       <c r="G27" t="n">
-        <v>8.449999999999999</v>
+        <v>8.07</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.05</v>
+        <v>-0.43</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
@@ -1450,34 +1450,34 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2268</v>
+        <v>1080</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
-        <v>46148</v>
+        <v>46169</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F28" t="n">
         <v>8.5</v>
       </c>
       <c r="G28" t="n">
-        <v>8.470000000000001</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.03</v>
+        <v>-0.46</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1490,34 +1490,34 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2269</v>
+        <v>1081</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>OLABARRIA, LINO [1987]</t>
+          <t>DUNN, CIERA E [6641]</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
-        <v>46149</v>
+        <v>46170</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>08:00 AM</t>
+          <t>08:30 AM</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>05:00 PM</t>
+          <t>05:30 PM</t>
         </is>
       </c>
       <c r="F29" t="n">
         <v>8.5</v>
       </c>
       <c r="G29" t="n">
-        <v>8.6</v>
+        <v>4.92</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1</v>
+        <v>-3.58</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -1530,7 +1530,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2270</v>
+        <v>2232</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
@@ -1538,7 +1538,7 @@
         </is>
       </c>
       <c r="C30" s="2" t="n">
-        <v>46150</v>
+        <v>46143</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1554,10 +1554,10 @@
         <v>8.5</v>
       </c>
       <c r="G30" t="n">
-        <v>8.49</v>
+        <v>8.51</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2271</v>
+        <v>2233</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
@@ -1578,26 +1578,16 @@
         </is>
       </c>
       <c r="C31" s="2" t="n">
-        <v>46151</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>01:00 PM</t>
-        </is>
+        <v>46144</v>
       </c>
       <c r="F31" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G31" t="n">
-        <v>4.05</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.95</v>
+        <v>0</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1610,7 +1600,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2272</v>
+        <v>2234</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1618,7 +1608,7 @@
         </is>
       </c>
       <c r="C32" s="2" t="n">
-        <v>46152</v>
+        <v>46145</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -1640,7 +1630,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2273</v>
+        <v>2235</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1648,7 +1638,7 @@
         </is>
       </c>
       <c r="C33" s="2" t="n">
-        <v>46153</v>
+        <v>46146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1664,10 +1654,10 @@
         <v>8.5</v>
       </c>
       <c r="G33" t="n">
-        <v>8.52</v>
+        <v>8.48</v>
       </c>
       <c r="H33" t="n">
-        <v>0.02</v>
+        <v>-0.02</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1680,7 +1670,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2274</v>
+        <v>2236</v>
       </c>
       <c r="B34" t="inlineStr">
         <is>
@@ -1688,16 +1678,26 @@
         </is>
       </c>
       <c r="C34" s="2" t="n">
-        <v>46154</v>
+        <v>46147</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F34" t="n">
-        <v>4</v>
+        <v>8.5</v>
       </c>
       <c r="G34" t="n">
-        <v>8.529999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="H34" t="n">
-        <v>4.53</v>
+        <v>-0.05</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
@@ -1710,7 +1710,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2275</v>
+        <v>2237</v>
       </c>
       <c r="B35" t="inlineStr">
         <is>
@@ -1718,7 +1718,7 @@
         </is>
       </c>
       <c r="C35" s="2" t="n">
-        <v>46155</v>
+        <v>46148</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -1734,10 +1734,10 @@
         <v>8.5</v>
       </c>
       <c r="G35" t="n">
-        <v>8.44</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1750,7 +1750,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2276</v>
+        <v>2238</v>
       </c>
       <c r="B36" t="inlineStr">
         <is>
@@ -1758,7 +1758,7 @@
         </is>
       </c>
       <c r="C36" s="2" t="n">
-        <v>46156</v>
+        <v>46149</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1774,10 +1774,10 @@
         <v>8.5</v>
       </c>
       <c r="G36" t="n">
-        <v>8.51</v>
+        <v>8.6</v>
       </c>
       <c r="H36" t="n">
-        <v>0.01</v>
+        <v>0.1</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1790,7 +1790,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2277</v>
+        <v>2239</v>
       </c>
       <c r="B37" t="inlineStr">
         <is>
@@ -1798,7 +1798,7 @@
         </is>
       </c>
       <c r="C37" s="2" t="n">
-        <v>46157</v>
+        <v>46150</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1814,10 +1814,10 @@
         <v>8.5</v>
       </c>
       <c r="G37" t="n">
-        <v>4.8</v>
+        <v>8.49</v>
       </c>
       <c r="H37" t="n">
-        <v>-3.7</v>
+        <v>-0.01</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1830,7 +1830,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2278</v>
+        <v>2240</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
@@ -1838,16 +1838,26 @@
         </is>
       </c>
       <c r="C38" s="2" t="n">
-        <v>46158</v>
+        <v>46151</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>01:00 PM</t>
+        </is>
       </c>
       <c r="F38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G38" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="H38" t="n">
-        <v>0</v>
+        <v>-0.95</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1860,7 +1870,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2279</v>
+        <v>2241</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
@@ -1868,7 +1878,7 @@
         </is>
       </c>
       <c r="C39" s="2" t="n">
-        <v>46159</v>
+        <v>46152</v>
       </c>
       <c r="F39" t="n">
         <v>0</v>
@@ -1890,7 +1900,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2280</v>
+        <v>2242</v>
       </c>
       <c r="B40" t="inlineStr">
         <is>
@@ -1898,7 +1908,7 @@
         </is>
       </c>
       <c r="C40" s="2" t="n">
-        <v>46160</v>
+        <v>46153</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1914,10 +1924,10 @@
         <v>8.5</v>
       </c>
       <c r="G40" t="n">
-        <v>4.22</v>
+        <v>8.52</v>
       </c>
       <c r="H40" t="n">
-        <v>-4.28</v>
+        <v>0.02</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1930,7 +1940,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2281</v>
+        <v>2243</v>
       </c>
       <c r="B41" t="inlineStr">
         <is>
@@ -1938,26 +1948,16 @@
         </is>
       </c>
       <c r="C41" s="2" t="n">
-        <v>46161</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
+        <v>46154</v>
       </c>
       <c r="F41" t="n">
-        <v>8.5</v>
+        <v>4</v>
       </c>
       <c r="G41" t="n">
         <v>8.529999999999999</v>
       </c>
       <c r="H41" t="n">
-        <v>0.03</v>
+        <v>4.53</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1970,7 +1970,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2282</v>
+        <v>2244</v>
       </c>
       <c r="B42" t="inlineStr">
         <is>
@@ -1978,7 +1978,7 @@
         </is>
       </c>
       <c r="C42" s="2" t="n">
-        <v>46162</v>
+        <v>46155</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -1994,10 +1994,10 @@
         <v>8.5</v>
       </c>
       <c r="G42" t="n">
-        <v>8.5</v>
+        <v>8.44</v>
       </c>
       <c r="H42" t="n">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2283</v>
+        <v>2245</v>
       </c>
       <c r="B43" t="inlineStr">
         <is>
@@ -2018,7 +2018,7 @@
         </is>
       </c>
       <c r="C43" s="2" t="n">
-        <v>46163</v>
+        <v>46156</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -2034,10 +2034,10 @@
         <v>8.5</v>
       </c>
       <c r="G43" t="n">
-        <v>8.57</v>
+        <v>8.51</v>
       </c>
       <c r="H43" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
@@ -2050,15 +2050,15 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2759</v>
+        <v>2246</v>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C44" s="2" t="n">
-        <v>46143</v>
+        <v>46157</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2074,10 +2074,10 @@
         <v>8.5</v>
       </c>
       <c r="G44" t="n">
-        <v>8.5</v>
+        <v>4.8</v>
       </c>
       <c r="H44" t="n">
-        <v>0</v>
+        <v>-3.7</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2090,15 +2090,15 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2760</v>
+        <v>2247</v>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
-        <v>46144</v>
+        <v>46158</v>
       </c>
       <c r="F45" t="n">
         <v>0</v>
@@ -2120,15 +2120,15 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2761</v>
+        <v>2248</v>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
-        <v>46145</v>
+        <v>46159</v>
       </c>
       <c r="F46" t="n">
         <v>0</v>
@@ -2150,15 +2150,15 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2762</v>
+        <v>2249</v>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
-        <v>46146</v>
+        <v>46160</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2174,10 +2174,10 @@
         <v>8.5</v>
       </c>
       <c r="G47" t="n">
-        <v>8.58</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H47" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2190,15 +2190,15 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2763</v>
+        <v>2250</v>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
-        <v>46147</v>
+        <v>46161</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -2214,10 +2214,10 @@
         <v>8.5</v>
       </c>
       <c r="G48" t="n">
-        <v>8.5</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>0.03</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2230,15 +2230,15 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2764</v>
+        <v>2251</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
-        <v>46148</v>
+        <v>46162</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -2254,10 +2254,10 @@
         <v>8.5</v>
       </c>
       <c r="G49" t="n">
-        <v>8.58</v>
+        <v>8.5</v>
       </c>
       <c r="H49" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2270,15 +2270,15 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2765</v>
+        <v>2252</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
-        <v>46149</v>
+        <v>46163</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2294,10 +2294,10 @@
         <v>8.5</v>
       </c>
       <c r="G50" t="n">
-        <v>8.5</v>
+        <v>8.57</v>
       </c>
       <c r="H50" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2310,15 +2310,15 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2766</v>
+        <v>2253</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
-        <v>46150</v>
+        <v>46164</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2334,10 +2334,10 @@
         <v>8.5</v>
       </c>
       <c r="G51" t="n">
-        <v>8.529999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="H51" t="n">
-        <v>0.03</v>
+        <v>-5</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2350,24 +2350,34 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2767</v>
+        <v>2254</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
-        <v>46151</v>
+        <v>46165</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F52" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>4.08</v>
       </c>
       <c r="H52" t="n">
-        <v>0</v>
+        <v>-4.42</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2380,15 +2390,15 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2768</v>
+        <v>2255</v>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C53" s="2" t="n">
-        <v>46152</v>
+        <v>46166</v>
       </c>
       <c r="F53" t="n">
         <v>0</v>
@@ -2410,15 +2420,15 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2769</v>
+        <v>2256</v>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C54" s="2" t="n">
-        <v>46153</v>
+        <v>46167</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -2434,10 +2444,10 @@
         <v>8.5</v>
       </c>
       <c r="G54" t="n">
-        <v>8.57</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>0.07000000000000001</v>
+        <v>-8.5</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2450,15 +2460,15 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2770</v>
+        <v>2257</v>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C55" s="2" t="n">
-        <v>46154</v>
+        <v>46168</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -2474,10 +2484,10 @@
         <v>8.5</v>
       </c>
       <c r="G55" t="n">
-        <v>8.58</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="H55" t="n">
-        <v>0.08</v>
+        <v>0.04</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2490,15 +2500,15 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2771</v>
+        <v>2258</v>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C56" s="2" t="n">
-        <v>46155</v>
+        <v>46169</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2514,10 +2524,10 @@
         <v>8.5</v>
       </c>
       <c r="G56" t="n">
-        <v>8.58</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="H56" t="n">
-        <v>0.08</v>
+        <v>0.37</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2530,15 +2540,15 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2772</v>
+        <v>2259</v>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+          <t>OLABARRIA, LINO [1987]</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
-        <v>46156</v>
+        <v>46170</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2554,10 +2564,10 @@
         <v>8.5</v>
       </c>
       <c r="G57" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>-8.5</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2570,7 +2580,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2773</v>
+        <v>2728</v>
       </c>
       <c r="B58" t="inlineStr">
         <is>
@@ -2578,7 +2588,7 @@
         </is>
       </c>
       <c r="C58" s="2" t="n">
-        <v>46157</v>
+        <v>46143</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2610,7 +2620,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2774</v>
+        <v>2729</v>
       </c>
       <c r="B59" t="inlineStr">
         <is>
@@ -2618,7 +2628,7 @@
         </is>
       </c>
       <c r="C59" s="2" t="n">
-        <v>46158</v>
+        <v>46144</v>
       </c>
       <c r="F59" t="n">
         <v>0</v>
@@ -2640,7 +2650,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2775</v>
+        <v>2730</v>
       </c>
       <c r="B60" t="inlineStr">
         <is>
@@ -2648,7 +2658,7 @@
         </is>
       </c>
       <c r="C60" s="2" t="n">
-        <v>46159</v>
+        <v>46145</v>
       </c>
       <c r="F60" t="n">
         <v>0</v>
@@ -2670,7 +2680,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2776</v>
+        <v>2731</v>
       </c>
       <c r="B61" t="inlineStr">
         <is>
@@ -2678,7 +2688,7 @@
         </is>
       </c>
       <c r="C61" s="2" t="n">
-        <v>46160</v>
+        <v>46146</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2694,10 +2704,10 @@
         <v>8.5</v>
       </c>
       <c r="G61" t="n">
-        <v>0</v>
+        <v>8.58</v>
       </c>
       <c r="H61" t="n">
-        <v>-8.5</v>
+        <v>0.08</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2710,7 +2720,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2777</v>
+        <v>2732</v>
       </c>
       <c r="B62" t="inlineStr">
         <is>
@@ -2718,7 +2728,7 @@
         </is>
       </c>
       <c r="C62" s="2" t="n">
-        <v>46161</v>
+        <v>46147</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2734,10 +2744,10 @@
         <v>8.5</v>
       </c>
       <c r="G62" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="H62" t="n">
-        <v>-8.5</v>
+        <v>0</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -2750,7 +2760,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2778</v>
+        <v>2733</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
@@ -2758,7 +2768,7 @@
         </is>
       </c>
       <c r="C63" s="2" t="n">
-        <v>46162</v>
+        <v>46148</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2774,10 +2784,10 @@
         <v>8.5</v>
       </c>
       <c r="G63" t="n">
-        <v>0</v>
+        <v>8.58</v>
       </c>
       <c r="H63" t="n">
-        <v>-8.5</v>
+        <v>0.08</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -2790,7 +2800,7 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2779</v>
+        <v>2734</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
@@ -2798,7 +2808,7 @@
         </is>
       </c>
       <c r="C64" s="2" t="n">
-        <v>46163</v>
+        <v>46149</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2814,10 +2824,10 @@
         <v>8.5</v>
       </c>
       <c r="G64" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="H64" t="n">
-        <v>-8.5</v>
+        <v>0</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -2830,15 +2840,15 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>3131</v>
+        <v>2735</v>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
-        <v>46143</v>
+        <v>46150</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2854,10 +2864,10 @@
         <v>8.5</v>
       </c>
       <c r="G65" t="n">
-        <v>8.550000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="H65" t="n">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -2870,34 +2880,24 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>3132</v>
+        <v>2736</v>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
-        <v>46144</v>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>01:00 PM</t>
-        </is>
+        <v>46151</v>
       </c>
       <c r="F66" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G66" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>-0.85</v>
+        <v>0</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -2910,15 +2910,15 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>3133</v>
+        <v>2737</v>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
-        <v>46145</v>
+        <v>46152</v>
       </c>
       <c r="F67" t="n">
         <v>0</v>
@@ -2940,15 +2940,15 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>3134</v>
+        <v>2738</v>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
-        <v>46146</v>
+        <v>46153</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -2964,10 +2964,10 @@
         <v>8.5</v>
       </c>
       <c r="G68" t="n">
-        <v>8.56</v>
+        <v>8.57</v>
       </c>
       <c r="H68" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -2980,15 +2980,15 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>3135</v>
+        <v>2739</v>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
-        <v>46147</v>
+        <v>46154</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3004,10 +3004,10 @@
         <v>8.5</v>
       </c>
       <c r="G69" t="n">
-        <v>8.550000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="H69" t="n">
-        <v>0.05</v>
+        <v>0.08</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3020,15 +3020,15 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>3136</v>
+        <v>2740</v>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
-        <v>46148</v>
+        <v>46155</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3044,10 +3044,10 @@
         <v>8.5</v>
       </c>
       <c r="G70" t="n">
-        <v>8.630000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="H70" t="n">
-        <v>0.13</v>
+        <v>0.08</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3060,15 +3060,15 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>3137</v>
+        <v>2741</v>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
-        <v>46149</v>
+        <v>46156</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3084,10 +3084,10 @@
         <v>8.5</v>
       </c>
       <c r="G71" t="n">
-        <v>8.550000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="H71" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3100,15 +3100,15 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>3138</v>
+        <v>2742</v>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
-        <v>46150</v>
+        <v>46157</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -3124,10 +3124,10 @@
         <v>8.5</v>
       </c>
       <c r="G72" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="H72" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3140,15 +3140,15 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>3139</v>
+        <v>2743</v>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
-        <v>46151</v>
+        <v>46158</v>
       </c>
       <c r="F73" t="n">
         <v>0</v>
@@ -3170,15 +3170,15 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>3140</v>
+        <v>2744</v>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
-        <v>46152</v>
+        <v>46159</v>
       </c>
       <c r="F74" t="n">
         <v>0</v>
@@ -3200,24 +3200,34 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>3141</v>
+        <v>2745</v>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
-        <v>46153</v>
+        <v>46160</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F75" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="G75" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H75" t="n">
-        <v>0</v>
+        <v>-8.5</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3230,21 +3240,31 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>3142</v>
+        <v>2746</v>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
-        <v>46154</v>
+        <v>46161</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
       </c>
       <c r="F76" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="G76" t="n">
-        <v>8</v>
+        <v>8.5</v>
       </c>
       <c r="H76" t="n">
         <v>0</v>
@@ -3260,15 +3280,15 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>3143</v>
+        <v>2747</v>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
-        <v>46155</v>
+        <v>46162</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -3284,10 +3304,10 @@
         <v>8.5</v>
       </c>
       <c r="G77" t="n">
-        <v>8.58</v>
+        <v>8.5</v>
       </c>
       <c r="H77" t="n">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3300,15 +3320,15 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>3144</v>
+        <v>2748</v>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
-        <v>46156</v>
+        <v>46163</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3324,10 +3344,10 @@
         <v>8.5</v>
       </c>
       <c r="G78" t="n">
-        <v>8.6</v>
+        <v>8.57</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3340,15 +3360,15 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>3145</v>
+        <v>2749</v>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
-        <v>46157</v>
+        <v>46164</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3380,15 +3400,15 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>3146</v>
+        <v>2750</v>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
-        <v>46158</v>
+        <v>46165</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -3410,15 +3430,15 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>3147</v>
+        <v>2751</v>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
-        <v>46159</v>
+        <v>46166</v>
       </c>
       <c r="F81" t="n">
         <v>0</v>
@@ -3440,15 +3460,15 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>3148</v>
+        <v>2752</v>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
-        <v>46160</v>
+        <v>46167</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3464,10 +3484,10 @@
         <v>8.5</v>
       </c>
       <c r="G82" t="n">
-        <v>8.550000000000001</v>
+        <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>0.05</v>
+        <v>-8.5</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -3480,15 +3500,15 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>3149</v>
+        <v>2753</v>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
-        <v>46161</v>
+        <v>46168</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3504,10 +3524,10 @@
         <v>8.5</v>
       </c>
       <c r="G83" t="n">
-        <v>8.460000000000001</v>
+        <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>-0.04</v>
+        <v>-8.5</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -3520,15 +3540,15 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>3150</v>
+        <v>2754</v>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SANCHEZ, ARMANDO [0895]</t>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
-        <v>46162</v>
+        <v>46169</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3544,10 +3564,10 @@
         <v>8.5</v>
       </c>
       <c r="G84" t="n">
-        <v>8.5</v>
+        <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>0</v>
+        <v>-8.5</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -3560,41 +3580,1071 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
+        <v>2755</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>RAMIREZ, ERIC FABIAN [6639]</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J85" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>3131</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G86" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J86" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>3132</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>01:00 PM</t>
+        </is>
+      </c>
+      <c r="F87" t="n">
+        <v>5</v>
+      </c>
+      <c r="G87" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-0.85</v>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J87" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>3133</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J88" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>3134</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F89" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G89" t="n">
+        <v>8.56</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J89" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>3135</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F90" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G90" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J90" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>3136</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F91" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G91" t="n">
+        <v>8.630000000000001</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J91" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>3137</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F92" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G92" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J92" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>3138</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F93" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G93" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J93" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>3139</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="F94" t="n">
+        <v>0</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J94" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>3140</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="F95" t="n">
+        <v>0</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J95" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>3141</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="n">
+        <v>46153</v>
+      </c>
+      <c r="F96" t="n">
+        <v>8</v>
+      </c>
+      <c r="G96" t="n">
+        <v>8</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J96" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>3142</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="F97" t="n">
+        <v>8</v>
+      </c>
+      <c r="G97" t="n">
+        <v>8</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J97" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>3143</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="n">
+        <v>46155</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F98" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G98" t="n">
+        <v>8.58</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J98" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>3144</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F99" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G99" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J99" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>3145</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F100" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G100" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J100" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>3146</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="F101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J101" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>3147</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="F102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J102" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>3148</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F103" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G103" t="n">
+        <v>8.550000000000001</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J103" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>3149</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F104" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G104" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="H104" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J104" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>3150</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F105" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G105" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J105" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
         <v>3151</v>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B106" t="inlineStr">
         <is>
           <t>SANCHEZ, ARMANDO [0895]</t>
         </is>
       </c>
-      <c r="C85" s="2" t="n">
+      <c r="C106" s="2" t="n">
         <v>46163</v>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>08:00 AM</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>05:00 PM</t>
-        </is>
-      </c>
-      <c r="F85" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="G85" t="n">
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F106" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G106" t="n">
         <v>8.48</v>
       </c>
-      <c r="H85" t="n">
+      <c r="H106" t="n">
         <v>-0.02</v>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>KATANA SALES</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J106" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>3152</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F107" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G107" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J107" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>3153</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="F108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J108" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>3154</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="F109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J109" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>3155</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="n">
+        <v>46167</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F110" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>-8.5</v>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J110" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>3156</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="n">
+        <v>46168</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F111" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G111" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J111" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>3157</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="n">
+        <v>46169</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F112" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G112" t="n">
+        <v>9.08</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J112" t="n">
+        <v>8618</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>3158</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SANCHEZ, ARMANDO [0895]</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="n">
+        <v>46170</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>08:00 AM</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>05:00 PM</t>
+        </is>
+      </c>
+      <c r="F113" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="G113" t="n">
+        <v>4.13</v>
+      </c>
+      <c r="H113" t="n">
+        <v>-4.37</v>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>KATANA SALES</t>
+        </is>
+      </c>
+      <c r="J113" t="n">
         <v>8618</v>
       </c>
     </row>
@@ -3641,13 +4691,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>149</v>
+        <v>191.5</v>
       </c>
       <c r="C2" t="n">
-        <v>134.98</v>
+        <v>175.58</v>
       </c>
       <c r="D2" t="n">
-        <v>-14.02</v>
+        <v>-15.92</v>
       </c>
     </row>
     <row r="3">
@@ -3657,13 +4707,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>128</v>
+        <v>179</v>
       </c>
       <c r="C3" t="n">
-        <v>123.67</v>
+        <v>152.98</v>
       </c>
       <c r="D3" t="n">
-        <v>-4.33</v>
+        <v>-26.02</v>
       </c>
     </row>
     <row r="4">
@@ -3673,13 +4723,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>127.5</v>
+        <v>170</v>
       </c>
       <c r="C4" t="n">
-        <v>93.92</v>
+        <v>128.06</v>
       </c>
       <c r="D4" t="n">
-        <v>-33.58</v>
+        <v>-41.94</v>
       </c>
     </row>
     <row r="5">
@@ -3689,13 +4739,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>131.5</v>
+        <v>174</v>
       </c>
       <c r="C5" t="n">
-        <v>131.33</v>
+        <v>161.85</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1699999999999999</v>
+        <v>-12.15</v>
       </c>
     </row>
   </sheetData>

--- a/sheet/8618.xlsx
+++ b/sheet/8618.xlsx
@@ -1514,10 +1514,10 @@
         <v>8.5</v>
       </c>
       <c r="G29" t="n">
-        <v>4.92</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="H29" t="n">
-        <v>-3.58</v>
+        <v>-0.46</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
@@ -4634,10 +4634,10 @@
         <v>8.5</v>
       </c>
       <c r="G113" t="n">
-        <v>4.13</v>
+        <v>8.66</v>
       </c>
       <c r="H113" t="n">
-        <v>-4.37</v>
+        <v>0.16</v>
       </c>
       <c r="I113" t="inlineStr">
         <is>
@@ -4694,10 +4694,10 @@
         <v>191.5</v>
       </c>
       <c r="C2" t="n">
-        <v>175.58</v>
+        <v>178.7</v>
       </c>
       <c r="D2" t="n">
-        <v>-15.92</v>
+        <v>-12.8</v>
       </c>
     </row>
     <row r="3">
@@ -4742,10 +4742,10 @@
         <v>174</v>
       </c>
       <c r="C5" t="n">
-        <v>161.85</v>
+        <v>166.38</v>
       </c>
       <c r="D5" t="n">
-        <v>-12.15</v>
+        <v>-7.619999999999999</v>
       </c>
     </row>
   </sheetData>
